--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.28941417190391</v>
+        <v>10.60952980293439</v>
       </c>
       <c r="D2" t="n">
-        <v>34.3296294649591</v>
+        <v>5.578564788055854</v>
       </c>
       <c r="E2" t="n">
-        <v>23.32885392048759</v>
+        <v>3.790938762079234</v>
       </c>
       <c r="F2" t="n">
-        <v>23.36128167701139</v>
+        <v>3.796208272514351</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>86.75226110289088</v>
+        <v>14.09724242921977</v>
       </c>
       <c r="D3" t="n">
-        <v>77.79567603152111</v>
+        <v>12.64179735512218</v>
       </c>
       <c r="E3" t="n">
-        <v>23.32885392048759</v>
+        <v>3.790938762079234</v>
       </c>
       <c r="F3" t="n">
-        <v>23.36128167701139</v>
+        <v>3.796208272514351</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.10945071864353</v>
+        <v>2.292785741779573</v>
       </c>
       <c r="D4" t="n">
-        <v>15.96237109870415</v>
+        <v>2.593885303539425</v>
       </c>
       <c r="E4" t="n">
-        <v>23.32885392048759</v>
+        <v>3.790938762079234</v>
       </c>
       <c r="F4" t="n">
-        <v>23.36128167701139</v>
+        <v>3.796208272514351</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.58241270732537</v>
+        <v>6.757142064940372</v>
       </c>
       <c r="D5" t="n">
-        <v>23.78967856538336</v>
+        <v>3.865822766874796</v>
       </c>
       <c r="E5" t="n">
-        <v>23.32885392048759</v>
+        <v>3.790938762079234</v>
       </c>
       <c r="F5" t="n">
-        <v>23.36128167701139</v>
+        <v>3.796208272514351</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.01945486712843</v>
+        <v>4.39066141590837</v>
       </c>
       <c r="D6" t="n">
-        <v>30.34324303341886</v>
+        <v>4.930776992930565</v>
       </c>
       <c r="E6" t="n">
-        <v>23.32885392048759</v>
+        <v>3.790938762079234</v>
       </c>
       <c r="F6" t="n">
-        <v>23.36128167701139</v>
+        <v>3.796208272514351</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.0038343099102</v>
+        <v>4.225623075360408</v>
       </c>
       <c r="D7" t="n">
-        <v>67.89695598597517</v>
+        <v>11.03325534772097</v>
       </c>
       <c r="E7" t="n">
-        <v>23.32885392048759</v>
+        <v>3.790938762079234</v>
       </c>
       <c r="F7" t="n">
-        <v>23.36128167701139</v>
+        <v>3.796208272514351</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.76180818702488</v>
+        <v>6.298793830391544</v>
       </c>
       <c r="D8" t="n">
-        <v>69.53094759800337</v>
+        <v>11.29877898467555</v>
       </c>
       <c r="E8" t="n">
-        <v>23.32885392048759</v>
+        <v>3.790938762079234</v>
       </c>
       <c r="F8" t="n">
-        <v>23.36128167701139</v>
+        <v>3.796208272514351</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
